--- a/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.79%1,034,000</t>
+          <t>9.02%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.79%</t>
+          <t>9.02%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.65%470,000</t>
+          <t>7.62%470,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.65%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5620</v>
+        <v>5440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.76%238,000</t>
+          <t>4.74%238,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5820</v>
+        <v>2315</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.59%221,000</t>
+          <t>4.32%510,197</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>221000</v>
+        <v>510197</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.46%377,000</t>
+          <t>4.30%377,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6400</v>
+        <v>5310</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.34%190,000</t>
+          <t>4.29%221,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>190000</v>
+        <v>221000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.33%227,000</t>
+          <t>4.25%227,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.19%1,209,000</t>
+          <t>4.21%1,209,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.21%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2270</v>
+        <v>6035</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.14%510,197</t>
+          <t>4.20%190,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>510197</v>
+        <v>190000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.59%470,000</t>
+          <t>3.58%470,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信 驊</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17885</v>
+        <v>1670</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.04%47,400</t>
+          <t>3.21%525,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>47400</v>
+        <v>525000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6187萬 潤</t>
+          <t>5274信 驊</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1250</v>
+        <v>17520</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.61%596,000</t>
+          <t>3.04%47,400</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>596000</v>
+        <v>47400</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6187萬 潤</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1620</v>
+        <v>1215</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.58%446,000</t>
+          <t>2.65%596,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.65%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>446000</v>
+        <v>596000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:04</t>
+          <t>2026-09-15 19:55:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.00%622,000</t>
+          <t>2.08%622,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.39%510</t>
+          <t>-3.82%490.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>510</v>
+        <v>490.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.88%1,034,000</t>
+          <t>1.86%1,034,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.7%154</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>154</v>
+        <v>1980</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%3,104,000</t>
+          <t>1.75%241,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3104000</v>
+        <v>241000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>-1.95%151</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1955</v>
+        <v>151</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.68%241,000</t>
+          <t>1.72%3,104,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>241000</v>
+        <v>3104000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.14%70.8</t>
+          <t>-3.53%68.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70.8</v>
+        <v>68.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.58%6,267,040</t>
+          <t>1.57%6,267,040</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>234</v>
+        <v>1840</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.56%1,861,000</t>
+          <t>1.53%227,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1861000</v>
+        <v>227000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1875</v>
+        <v>221.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.52%227,000</t>
+          <t>1.51%1,861,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>227000</v>
+        <v>1861000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.38%378,000</t>
+          <t>1.34%378,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-3.85%2625</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2580</v>
+        <v>2625</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.19%122,000</t>
+          <t>1.17%122,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>+0.26%192.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>142.5</v>
+        <v>192.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.07%2,096,000</t>
+          <t>1.08%1,532,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2096000</v>
+        <v>1532000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.75%731</t>
+          <t>-0.68%726</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.05%404,000</t>
+          <t>1.07%404,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.52%192</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>192</v>
+        <v>138.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.05%1,532,000</t>
+          <t>1.06%2,096,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1532000</v>
+        <v>2096000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.07%237</t>
+          <t>+0.12%82.9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>237</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.99%1,169,000</t>
+          <t>1.00%3,309,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1169000</v>
+        <v>3309000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.96%82.8</t>
+          <t>-1.48%233.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>82.8</v>
+        <v>233.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.98%3,309,000</t>
+          <t>1.00%1,169,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3309000</v>
+        <v>1169000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:06</t>
+          <t>2026-09-15 19:55:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>261.5</v>
+        <v>257</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.93%999,000</t>
+          <t>0.94%999,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.79%1590</t>
+          <t>-5.03%1510</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-5.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1590</v>
+        <v>1510</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.93%163,000</t>
+          <t>0.90%163,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6274台 燿</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-1.13%218.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1365</v>
+        <v>218.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.88%175,000</t>
+          <t>0.89%1,107,336</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>175000</v>
+        <v>1107336</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>6274台 燿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.23%221</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>221</v>
+        <v>1370</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.87%1,107,336</t>
+          <t>0.88%175,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1107336</v>
+        <v>175000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7750新 代</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.75%1960</t>
+          <t>-0.8%246.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1960</v>
+        <v>246.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.85%122,000</t>
+          <t>0.87%960,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>122000</v>
+        <v>960000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>248.5</v>
+        <v>6055</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.85%960,000</t>
+          <t>0.86%39,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>960000</v>
+        <v>39000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>7750新 代</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>-3.57%1890</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5995</v>
+        <v>1890</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.84%39,000</t>
+          <t>0.84%122,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>39000</v>
+        <v>122000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2810</v>
+        <v>2675</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-4.08%153</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.77%1,351,000</t>
+          <t>0.76%1,351,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>3374精 材</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-7.01%531</t>
+          <t>-4.89%408.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.01%</t>
+          <t>-4.89%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>531</v>
+        <v>408.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.57%293,000</t>
+          <t>0.51%340,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>293000</v>
+        <v>340000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3374精 材</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-5.02%463.5</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>463.5</v>
+        <v>6310</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.52%340,000</t>
+          <t>0.48%21,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>340000</v>
+        <v>21000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>7769鴻 勁</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-2.7%6135</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6600</v>
+        <v>6135</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.50%21,000</t>
+          <t>0.45%20,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7769鴻 勁</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.08%6305</t>
+          <t>-0.37%537</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6305</v>
+        <v>537</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.45%20,000</t>
+          <t>0.39%200,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+2.28%539</t>
+          <t>-2.75%159</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+2.28%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>539</v>
+        <v>159</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.39%200,000</t>
+          <t>0.34%592,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>200000</v>
+        <v>592000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>3293鈊 象</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.31%163.5</t>
+          <t>-0.43%696</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>163.5</v>
+        <v>696</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.35%592,000</t>
+          <t>0.34%133,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>592000</v>
+        <v>133000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:07</t>
+          <t>2026-09-15 19:55:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.17%810</t>
+          <t>-2.22%792</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:08</t>
+          <t>2026-09-15 19:55:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3293鈊 象</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.56%693</t>
+          <t>-4.06%96.9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-4.06%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>693</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.33%133,000</t>
+          <t>0.30%834,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>133000</v>
+        <v>834000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:08</t>
+          <t>2026-09-15 19:55:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,34 +3310,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%101</t>
+          <t>+0.45%221</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.30%834,000</t>
+          <t>0.27%340,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>834000</v>
+        <v>340000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:08</t>
+          <t>2026-09-15 19:55:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>6121新 普</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0%220</t>
+          <t>-1.58%373</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>220</v>
+        <v>373</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.27%340,000</t>
+          <t>0.24%178,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>340000</v>
+        <v>178000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:08</t>
+          <t>2026-09-15 19:55:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6121新 普</t>
+          <t>9939宏全</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.53%380.5</t>
+          <t>-0.4%125.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>380.5</v>
+        <v>125.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.24%178,000</t>
+          <t>0.08%180,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>178000</v>
+        <v>180000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:08</t>
+          <t>2026-09-15 19:55:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>9939宏全</t>
+          <t>1215卜蜂</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.7%126</t>
+          <t>-1.86%105.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>126</v>
+        <v>105.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.08%180,000</t>
+          <t>0.08%200,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>180000</v>
+        <v>200000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3528,67 +3528,6 @@
         </is>
       </c>
       <c r="M51" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-09-15 00:03:08</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1215卜蜂</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-2.71%107.5</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-2.71%</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0.08%200,000</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:26</t>
+          <t>2026-09-15 21:13:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:28</t>
+          <t>2026-09-15 21:13:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:29</t>
+          <t>2026-09-15 21:13:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:30</t>
+          <t>2026-09-15 21:13:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:30</t>
+          <t>2026-09-15 21:13:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:30</t>
+          <t>2026-09-15 21:13:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:30</t>
+          <t>2026-09-15 21:13:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:55:30</t>
+          <t>2026-09-15 21:13:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:32</t>
+          <t>2026-09-15 22:23:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:34</t>
+          <t>2026-09-15 22:23:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:35</t>
+          <t>2026-09-15 22:23:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:36</t>
+          <t>2026-09-15 22:23:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:36</t>
+          <t>2026-09-15 22:23:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:36</t>
+          <t>2026-09-15 22:23:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:36</t>
+          <t>2026-09-15 22:23:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:36</t>
+          <t>2026-09-15 22:23:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:49</t>
+          <t>2026-09-15 22:30:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:51</t>
+          <t>2026-09-15 22:30:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:52</t>
+          <t>2026-09-15 22:30:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:53</t>
+          <t>2026-09-15 22:30:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:53</t>
+          <t>2026-09-15 22:30:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:53</t>
+          <t>2026-09-15 22:30:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:53</t>
+          <t>2026-09-15 22:30:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:53</t>
+          <t>2026-09-15 22:30:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
